--- a/Resultados_Ajuste_Mercado_Financiero (trabajado).xlsx
+++ b/Resultados_Ajuste_Mercado_Financiero (trabajado).xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Completos" sheetId="1" state="visible" r:id="rId2"/>
@@ -165,6 +165,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -186,6 +187,7 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -193,6 +195,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2079,7 +2082,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="0" width="8.54"/>
   </cols>
@@ -2447,7 +2450,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3294,7 +3297,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3925,7 +3928,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.16"/>
   </cols>
